--- a/forms/trg/Formulir_TRG_apm.xlsx
+++ b/forms/trg/Formulir_TRG_apm.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B33)</f>
+        <f>COUNTA(Anggota!B5:B34)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F33)</f>
+        <f>COUNTA(Anggota!F5:F34)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,22 +913,14 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Asharin Juwita Purisamya, SE, MSc., CWM.</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
+          <t>Prof. Dr. Mediaty, SE., M.Si., Ak, CA, CWM.</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="n"/>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Accounting and Finance</t>
+          <t>Public Management Accounting</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -937,11 +929,15 @@
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-9037-756X</t>
+          <t>0000-0003-3314-4900</t>
         </is>
       </c>
       <c r="K5" s="12" t="n"/>
-      <c r="L5" s="12" t="n"/>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>57192190531</t>
+        </is>
+      </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -954,12 +950,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Dr. Rahmawati HS, SE, M. Si, Ak, CA, ASEAN CPA</t>
+          <t>Asharin Juwita Purisamya, SE, MSc., CWM.</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -969,7 +965,7 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Accounting</t>
+          <t>Accounting and Finance</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -978,15 +974,11 @@
       <c r="I6" s="12" t="n"/>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-1457-7914</t>
+          <t>0000-0002-9037-756X</t>
         </is>
       </c>
       <c r="K6" s="12" t="n"/>
-      <c r="L6" s="11" t="inlineStr">
-        <is>
-          <t>57226838208</t>
-        </is>
-      </c>
+      <c r="L6" s="12" t="n"/>
       <c r="M6" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -999,12 +991,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Dr. Rahmat Muhammad, M.Si</t>
+          <t>Dr. Rahmawati HS, SE, M. Si, Ak, CA, ASEAN CPA</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1014,7 +1006,7 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Political Sosialogy</t>
+          <t>Accounting</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1023,13 +1015,13 @@
       <c r="I7" s="12" t="n"/>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-1535-1060</t>
+          <t>0000-0002-1457-7914</t>
         </is>
       </c>
       <c r="K7" s="12" t="n"/>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>58952197000</t>
+          <t>57226838208</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
@@ -1044,12 +1036,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Grace T. Pontoh, SE., M. Si, Ak., CA.</t>
+          <t>Dr. Rahmat Muhammad, M.Si</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1059,7 +1051,7 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Accounting Information System</t>
+          <t>Political Sosialogy</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1068,13 +1060,13 @@
       <c r="I8" s="12" t="n"/>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-6672-5408</t>
+          <t>0000-0002-1535-1060</t>
         </is>
       </c>
       <c r="K8" s="12" t="n"/>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>57201193981</t>
+          <t>58952197000</t>
         </is>
       </c>
       <c r="M8" s="11" t="inlineStr">
@@ -1089,12 +1081,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Dr. Nadhirah Nagu, S.E.,Ak, M.Si, Ak, CA.</t>
+          <t>Prof. Dr. Grace T. Pontoh, SE., M. Si, Ak., CA.</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1104,7 +1096,7 @@
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Sustainability Accounting and Sustainability Assurance</t>
+          <t>Accounting Information System</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -1113,13 +1105,13 @@
       <c r="I9" s="12" t="n"/>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-0759-1435</t>
+          <t>0000-0001-6672-5408</t>
         </is>
       </c>
       <c r="K9" s="12" t="n"/>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>57204477667</t>
+          <t>57201193981</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
@@ -1134,12 +1126,12 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Dr. Agus Bandang, M.Si., Ak., CA.</t>
+          <t>Dr. Nadhirah Nagu, S.E.,Ak, M.Si, Ak, CA.</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1149,18 +1141,22 @@
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Management Accounting</t>
+          <t>Sustainability Accounting and Sustainability Assurance</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
       <c r="G10" s="12" t="n"/>
       <c r="H10" s="12" t="n"/>
       <c r="I10" s="12" t="n"/>
-      <c r="J10" s="12" t="n"/>
+      <c r="J10" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-0759-1435</t>
+        </is>
+      </c>
       <c r="K10" s="12" t="n"/>
       <c r="L10" s="11" t="inlineStr">
         <is>
-          <t>57204549817</t>
+          <t>57204477667</t>
         </is>
       </c>
       <c r="M10" s="11" t="inlineStr">
@@ -1175,17 +1171,17 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Professor Dr Rozainun Haji Abdul Aziz P.M.K. CA(M)</t>
+          <t>Dr. Agus Bandang, M.Si., Ak., CA.</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>UniKL Business School</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
@@ -1197,15 +1193,11 @@
       <c r="G11" s="12" t="n"/>
       <c r="H11" s="12" t="n"/>
       <c r="I11" s="12" t="n"/>
-      <c r="J11" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-2699-298X</t>
-        </is>
-      </c>
+      <c r="J11" s="12" t="n"/>
       <c r="K11" s="12" t="n"/>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>35368249000</t>
+          <t>57204549817</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
@@ -1220,22 +1212,22 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Ir. Fadli Syamsudin, MSc.</t>
+          <t>Professor Dr Rozainun Haji Abdul Aziz P.M.K. CA(M)</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>National Research and Innovation Agency - Badan Riset dan Inovasi Nasional (BRIN)</t>
+          <t>UniKL Business School</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Blue Accounting</t>
+          <t>Management Accounting</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
@@ -1244,13 +1236,13 @@
       <c r="I12" s="12" t="n"/>
       <c r="J12" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-6240-8568</t>
+          <t>0000-0002-2699-298X</t>
         </is>
       </c>
       <c r="K12" s="12" t="n"/>
       <c r="L12" s="11" t="inlineStr">
         <is>
-          <t>24399716000</t>
+          <t>35368249000</t>
         </is>
       </c>
       <c r="M12" s="11" t="inlineStr">
@@ -1265,31 +1257,39 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Faisal Abdullah, PhD</t>
+          <t>Prof. Dr. Ir. Fadli Syamsudin, MSc.</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Adelaide University</t>
+          <t>National Research and Innovation Agency - Badan Riset dan Inovasi Nasional (BRIN)</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Financial Accounting</t>
+          <t>Blue Accounting</t>
         </is>
       </c>
       <c r="F13" s="12" t="n"/>
       <c r="G13" s="12" t="n"/>
       <c r="H13" s="12" t="n"/>
       <c r="I13" s="12" t="n"/>
-      <c r="J13" s="12" t="n"/>
+      <c r="J13" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-6240-8568</t>
+        </is>
+      </c>
       <c r="K13" s="12" t="n"/>
-      <c r="L13" s="12" t="n"/>
+      <c r="L13" s="11" t="inlineStr">
+        <is>
+          <t>24399716000</t>
+        </is>
+      </c>
       <c r="M13" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1302,22 +1302,22 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Alliah Grace D. Gubangco</t>
+          <t>Faisal Abdullah, PhD</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>University of Santo Tomas</t>
+          <t>Adelaide University</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Accounting and Corporate Governance</t>
+          <t>Financial Accounting</t>
         </is>
       </c>
       <c r="F14" s="12" t="n"/>
@@ -1339,39 +1339,31 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Anis Anshari Mas'ud, S.Kom., M.M.</t>
+          <t>Alliah Grace D. Gubangco</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Sulawesi Barat University</t>
+          <t>University of Santo Tomas</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Digital Business</t>
+          <t>Accounting and Corporate Governance</t>
         </is>
       </c>
       <c r="F15" s="12" t="n"/>
       <c r="G15" s="12" t="n"/>
       <c r="H15" s="12" t="n"/>
       <c r="I15" s="12" t="n"/>
-      <c r="J15" s="11" t="inlineStr">
-        <is>
-          <t>my-orcid?orcid=0000-0003-2985-490X</t>
-        </is>
-      </c>
+      <c r="J15" s="12" t="n"/>
       <c r="K15" s="12" t="n"/>
-      <c r="L15" s="11" t="inlineStr">
-        <is>
-          <t>59133070200</t>
-        </is>
-      </c>
+      <c r="L15" s="12" t="n"/>
       <c r="M15" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1384,31 +1376,39 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Yusfi Tsabita Nanda Yusuf</t>
+          <t>Anis Anshari Mas'ud, S.Kom., M.M.</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Sulawesi Barat University</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>Master Postgraduate Student</t>
+          <t>Digital Business</t>
         </is>
       </c>
       <c r="F16" s="12" t="n"/>
       <c r="G16" s="12" t="n"/>
       <c r="H16" s="12" t="n"/>
       <c r="I16" s="12" t="n"/>
-      <c r="J16" s="12" t="n"/>
+      <c r="J16" s="11" t="inlineStr">
+        <is>
+          <t>my-orcid?orcid=0000-0003-2985-490X</t>
+        </is>
+      </c>
       <c r="K16" s="12" t="n"/>
-      <c r="L16" s="12" t="n"/>
+      <c r="L16" s="11" t="inlineStr">
+        <is>
+          <t>59133070200</t>
+        </is>
+      </c>
       <c r="M16" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1421,12 +1421,12 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Gabriella Shalisha Citra Harvie</t>
+          <t>Yusfi Tsabita Nanda Yusuf</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Nurhalijah</t>
+          <t>Gabriella Shalisha Citra Harvie</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
@@ -1495,12 +1495,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Annisa Aini Hadjar</t>
+          <t>Nurhalijah</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>Asnawir</t>
+          <t>Annisa Aini Hadjar</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>Doctoral Postgraduate Student</t>
+          <t>Master Postgraduate Student</t>
         </is>
       </c>
       <c r="F20" s="12" t="n"/>
@@ -1569,12 +1569,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>Ulfanita Arsyam</t>
+          <t>Asnawir</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>Master Postgraduate Student</t>
+          <t>Doctoral Postgraduate Student</t>
         </is>
       </c>
       <c r="F21" s="12" t="n"/>
@@ -1604,10 +1604,26 @@
       <c r="A22" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="12" t="n"/>
-      <c r="C22" s="12" t="n"/>
-      <c r="D22" s="12" t="n"/>
-      <c r="E22" s="11" t="n"/>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>Ulfanita Arsyam</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>Master Postgraduate Student</t>
+        </is>
+      </c>
       <c r="F22" s="12" t="n"/>
       <c r="G22" s="12" t="n"/>
       <c r="H22" s="12" t="n"/>
@@ -1615,7 +1631,11 @@
       <c r="J22" s="12" t="n"/>
       <c r="K22" s="12" t="n"/>
       <c r="L22" s="12" t="n"/>
-      <c r="M22" s="12" t="n"/>
+      <c r="M22" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -1804,15 +1824,32 @@
       <c r="L33" s="12" t="n"/>
       <c r="M33" s="12" t="n"/>
     </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="12" t="n"/>
+      <c r="C34" s="12" t="n"/>
+      <c r="D34" s="12" t="n"/>
+      <c r="E34" s="11" t="n"/>
+      <c r="F34" s="12" t="n"/>
+      <c r="G34" s="12" t="n"/>
+      <c r="H34" s="12" t="n"/>
+      <c r="I34" s="12" t="n"/>
+      <c r="J34" s="12" t="n"/>
+      <c r="K34" s="12" t="n"/>
+      <c r="L34" s="12" t="n"/>
+      <c r="M34" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>

--- a/forms/trg/Formulir_TRG_apm.xlsx
+++ b/forms/trg/Formulir_TRG_apm.xlsx
@@ -916,7 +916,11 @@
           <t>Prof. Dr. Mediaty, SE., M.Si., Ak, CA, CWM.</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
       <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
